--- a/수련지도_입력양식_성원재_김용성.xlsx
+++ b/수련지도_입력양식_성원재_김용성.xlsx
@@ -1010,7 +1010,7 @@
     <col width="27.125" customWidth="1" style="21" min="1" max="1"/>
     <col width="22" customWidth="1" style="21" min="3" max="3"/>
     <col width="20.75" customWidth="1" style="21" min="4" max="4"/>
-    <col width="110" customWidth="1" style="21" min="5" max="5"/>
+    <col width="80" customWidth="1" style="21" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="21">
@@ -1040,7 +1040,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="409" customHeight="1" s="21">
+    <row r="2" ht="228" customHeight="1" s="21">
       <c r="A2" s="11" t="inlineStr">
         <is>
           <t>책임 지도전문의</t>
@@ -1063,54 +1063,16 @@
       </c>
       <c r="E2" s="26" t="inlineStr">
         <is>
-          <t>7/1 수련지도 : 뇌경색 환자 평가: NIHSS, rtPA/ERT 기준(평가 5/4점)(송준규, 박예지, 박은지, 유홍근)
-7/2 수련지도 : 전공의 강의 - Chemical Signaling in the Nervous System 북리딩(Glutamate, Acetylcholine 등)(송준규, 박예지, 박은지, 유홍근)
-7/3 개별 면담 : 수련·근무/학습·역량: 9월 전공의 교대·업무 변경, 연차별 주 1회 당직 변경 안내(박예지, 박은지, 유홍근)
-7/3 수련지도 : 응급실 진료 지도: 신경계 이상 증상 환자의 진찰·영상 판독·처치 참관(유홍근)
-7/6 수련지도 : 외래 진료 참관 및 교육: 운동신경세포병 보호자 설명(평가 4점)(유홍근)
-7/8 수련지도 : 응급실 진료 지도: 두통 원인 진단·평가, 약물(혈관확장제) 유발 두통(평가 5점)(송준규, 박은지)
-7/9 수련지도 : 전공의 강의: 뇌실, 맥락얼기, 뇌척수액(송준규, 박예지, 박은지, 유홍근)
-7/10 개별 면담 : 수련·근무/학습·역량: 수련 상황, 하계 휴가 일정, 휴가 중 업무 전가 방지 약속(송준규, 박예지, 박은지, 유홍근)
-7/13 수련지도 : 외래 진료 교육: 상완신경총병증 환자 신경생리검사·MRI 종합 설명(평가 4점)(유홍근)
-7/14 간담회 : 지도전문의-전공의 간담회: 연차별 2학기 전공의 스케줄·휴가 일정 조정 완료(송준규, 박예지, 유홍근)
-7/15 수련지도 : 응급실 진료 지도: 어지럼증 환자 문진·신경계 진찰·영상 확인(박예지)
-7/16 수련지도 : 전공의 교육: 뇌실·맥락얼기·뇌척수액 강의 이어서 진행(송준규, 박예지, 유홍근)
-7/20 수련지도 : 외래 진료 교육: 원인 미상 근력이상 추적 신경생리검사 판독·설명(평가 4점)(송준규)
-7/22 수련지도 : 치매안심센터 진료: 인지기능검사 domain별 해석, CDR 평가(평가 3점)(유홍근)
-7/23 수련지도 : 전공의 교육: 뇌막(Meninges) 해부 강의(송준규, 박예지, 박은지, 유홍근)
-7/24 개별 면담 : 학습·역량: 본원 입원환자 접근 방법, 수석 전공의 중심 입원환자 리뷰·발표(송준규, 박예지, 박은지, 유홍근)
-7/27 수련지도 : 외래 진료 교육: 자가면역 말초신경병증 양상·신경생리검사 결과(유홍근)
-7/29 수련지도 : 병동 환자 교육: 신경근육질환 입원환자 진찰·진단 과정(박예지, 박은지)
-7/30 수련지도 : 전공의 교육: 뇌수막 이상 관련 질환(송준규, 박예지, 박은지, 유홍근)
-7/31 개별 면담 : 진로·진학: 의국 출신 전문의 진로 안내(송준규, 박예지, 박은지, 유홍근)
-8/3 수련지도 : 외래 진료 교육: 경추·요추 근뿌리병증 병력 청취·진찰·검사 해석(평가 4점)(송준규)
-8/5 개별 면담 : 수련·근무/생활·심리: 개별 면담으로 고충·학습 현황 청취, 적극적 학습 권유(송준규, 박예지, 박은지, 유홍근)
-8/6 수련지도 : 전공의 교육: 뇌혈관 해부학 강의(Chap 8)(송준규, 박예지, 박은지, 유홍근)
-8/10 수련지도 : 외래 진료 교육: 루게릭병 환자 외래 진료 및 보호자 교육(송준규)
-8/12 수련지도 : 응급실 진료 지도: 두통환자 문진·진찰·영상 해석, 외래 추적 시 주의점(박예지, 박은지)
-8/13 수련지도 : 전공의 교육: 본원 내원 뇌졸중 환자 증례 보고 및 시사점 논의(송준규, 박예지, 박은지)
-8/14 개별 면담 : 기타: 의정사태 이후 변화된 환경에 대한 사직 전공의 고충 청취(송준규, 박예지, 박은지)
-8/31 수련지도 : 외래 진료 교육: 중증근무력증 환자 평가(MG-ADL 등), Level 2(유홍근)
-9/1 수련지도 : 전공의 교육: 척수 해부학(Chap 9)(박은지, 신정욱)
-9/2 수련지도 : 치매안심센터 진료 교육: CIST, CERAD 평가 방법·결과 의의, Level 1(박은지)
-9/3 간담회 : 2학기 학회(심포지움) 참석 스케줄 논의: WSC, MDS, IC-KNA 가급적 참석 결정(참석 김영서)(신정욱, 박은지)
-9/4 개별 면담 : 수련·근무/학습·역량: 2학기 수련·업무 방향, 교육활동·임상신경생리검사 학습 주안점(신정욱, 박은지)
-9/7 수련지도 : 외래 진료 교육: ALS 병기 평가(ALSFRS-R, King's stage), Level 4(박은지)
-9/8 수련지도 : 전공의 교육: 척수 부위 질환 해부학 지식 및 강의(신정욱, 박은지)
-9/9 수련지도 : 응급실 진료 지도: 급성뇌경색 처치·치료 알고리즘, Level 4 이상(박은지)
-9/10 간담회 : 2학기 원내 학술활동 일정 논의: 토픽·저널 컨퍼런스, 지도전문의 강의 스케줄 가안 확정(참석 김영서)((대상 전공의 미기재))
-9/11 개별 면담 : 진로·진학: 전문의 시험 이후 일정, 전문적 업무분장(신정욱, 박은지)
-9/14 수련지도 : 외래 진료 교육: NMOSD 환자 병력 청취·신경계 진찰, Level 4(박은지)
-9/15 수련지도 : 전공의 교육: NMOSD 증례 및 진단 기준 강의(신정욱, 박은지)
-9/16 수련지도 : 치매안심센터 진료 교육: 치매/경도인지장애 병력 청취·CDR 평가, Level 3(박은지)
-9/17 수련지도 : 전공의 교육: 레비소체치매 증례 소개 및 주요 증상(참석 강성우 포함)(박은지, 신정욱)
-9/18 개별 면담 : 수련·근무: 당직 애로사항 청취, 지도전문의에게 도움 요청 지도(신정욱, 박은지)
-9/21 수련지도 : 외래 진료 교육: 외래 진료 참관(유홍근)
-9/21 개별 면담 : 수련·근무: 수련 현황, 업무 분장, 당직 체계 논의(박은지)
-9/22 학술집담회 : 원내 컨퍼런스 - 증례 발표: 박은지 NMOSD 증례 및 치료 가이드라인(신정욱, 박은지)
-9/23 수련지도 : 치매안심센터 진료 교육: 지역사회 경도인지장애·치매 환자 관리, 진료 참관(신정욱)
-9/28 수련지도 : 외래 진료 교육: 영양결핍 신경계 질환 진찰·병력 청취·검사(박은지)
-9/29 수련지도 : 전공의 교육: Lateral medullary syndrome 증례(참석 정수 포함)(박은지, 신정욱)</t>
+          <t>7월 수련지도 : 15건 (전공의 강의·교육 5, 외래 진료교육 4, 응급실 진료지도 3, 증례 평가 1, 치매안심센터 진료 1, 병동 환자교육 1)
+7월 간담회 : 1건
+7월 개별 면담 : 4건 (분야별: 수련·근무 2, 학습·역량 3, 진로·진학 1)
+8월 수련지도 : 6건 (외래 진료교육 3, 전공의 강의·교육 2, 응급실 진료지도 1)
+8월 개별 면담 : 2건 (분야별: 수련·근무 1, 생활·심리 1, 기타 1)
+9월 수련지도 : 13건 (전공의 강의·교육 5, 외래 진료교육 4, 치매안심센터 진료 3, 응급실 진료지도 1)
+9월 학술집담회 : 1건
+9월 간담회 : 2건
+9월 개별 면담 : 4건 (분야별: 수련·근무 3, 학습·역량 1, 진로·진학 1)
+합계 : 48건</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1091,7 @@
       <c r="D3" s="14" t="n"/>
       <c r="E3" s="15" t="n"/>
     </row>
-    <row r="4" ht="323" customHeight="1" s="21">
+    <row r="4" ht="76" customHeight="1" s="21">
       <c r="A4" s="11" t="inlineStr">
         <is>
           <t>교육전담</t>
@@ -1152,20 +1114,10 @@
       </c>
       <c r="E4" s="27" t="inlineStr">
         <is>
-          <t>7/6 수련지도 : 신경생리검사 판독 및 교육(평가 3점)(송준규)
-7/13 수련지도 : Peroneal neuropathy 북리딩(Preston 25), 발표·토론(평가 1점)(송준규, 박예지, 박은지, 유홍근)
-7/13 수련지도 : 신경생리검사 판독 및 교육(평가 3점)(송준규)
-7/20 수련지도 : 신경생리검사 판독 및 교육(평가 3점)(송준규)
-7/27 수련지도 : Femoral neuropathy 북리딩(Preston 26), 발표·토론(평가 1점)(송준규, 박예지, 박은지, 유홍근)
-7/27 수련지도 : 신경생리검사 판독 및 교육(평가 3점)(송준규)
-8/10 수련지도 : Tarsal tunnel syndrome 북리딩(Preston 27), 발표·토론(평가 1점)(송준규, 박예지, 박은지, 유홍근)
-8/10 수련지도 : 신경생리검사 판독 및 교육(평가 3점)(송준규)
-8/28 수련지도 : Facial and Trigeminal neuropathy 북리딩(Preston 28), 발표·토론(평가 1점)(송준규, 박예지, 박은지, 유홍근)
-8/28 수련지도 : 신경생리검사 판독 및 교육(평가 3점)(송준규)
-9/7 수련지도 : 신경생리검사 판독 및 교육, 2시간(평가 3점)(신정욱)
-9/14 수련지도 : 신경생리검사 판독 및 교육, 2시간(평가 3점)(신정욱)
-9/21 수련지도 : Polyneuropathy 북리딩(Preston), 발표·토론(평가 1점)(신정욱, 박은지)
-9/21 수련지도 : 신경생리검사 판독 및 교육, 2시간(평가 3점)(신정욱)</t>
+          <t>7월 수련지도 : 6건 (신경생리검사 판독교육 4, 북리딩 2)
+8월 수련지도 : 4건 (북리딩 2, 신경생리검사 판독교육 2)
+9월 수련지도 : 4건 (신경생리검사 판독교육 3, 북리딩 1)
+합계 : 14건</t>
         </is>
       </c>
     </row>

--- a/수련지도_입력양식_성원재_김용성.xlsx
+++ b/수련지도_입력양식_성원재_김용성.xlsx
@@ -248,7 +248,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -257,7 +257,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -646,7 +646,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="23.125" customWidth="1" style="21" min="3" max="3"/>
-    <col width="95" customWidth="1" style="21" min="4" max="4"/>
+    <col width="70" customWidth="1" style="21" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1" ht="51.75" customHeight="1" s="21">
@@ -671,7 +671,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="462" customHeight="1" s="21">
+    <row r="2" ht="108" customHeight="1" s="21">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>’26.7월</t>
@@ -687,33 +687,15 @@
       </c>
       <c r="D2" s="22" t="inlineStr">
         <is>
-          <t>[성원재 15건]
-· 7/1 뇌경색 환자 평가: NIHSS, rtPA/ERT 기준(평가 5/4점) (송준규, 박예지, 박은지, 유홍근)
-· 7/2 전공의 강의 - Chemical Signaling in the Nervous System 북리딩(Glutamate, Acetylcholine 등) (송준규, 박예지, 박은지, 유홍근)
-· 7/3 응급실 진료 지도: 신경계 이상 증상 환자의 진찰·영상 판독·처치 참관 (유홍근)
-· 7/6 외래 진료 참관 및 교육: 운동신경세포병 보호자 설명(평가 4점) (유홍근)
-· 7/8 응급실 진료 지도: 두통 원인 진단·평가, 약물(혈관확장제) 유발 두통(평가 5점) (송준규, 박은지)
-· 7/9 전공의 강의: 뇌실, 맥락얼기, 뇌척수액 (송준규, 박예지, 박은지, 유홍근)
-· 7/13 외래 진료 교육: 상완신경총병증 환자 신경생리검사·MRI 종합 설명(평가 4점) (유홍근)
-· 7/15 응급실 진료 지도: 어지럼증 환자 문진·신경계 진찰·영상 확인 (박예지)
-· 7/16 전공의 교육: 뇌실·맥락얼기·뇌척수액 강의 이어서 진행 (송준규, 박예지, 유홍근)
-· 7/20 외래 진료 교육: 원인 미상 근력이상 추적 신경생리검사 판독·설명(평가 4점) (송준규)
-· 7/22 치매안심센터 진료: 인지기능검사 domain별 해석, CDR 평가(평가 3점) (유홍근)
-· 7/23 전공의 교육: 뇌막(Meninges) 해부 강의 (송준규, 박예지, 박은지, 유홍근)
-· 7/27 외래 진료 교육: 자가면역 말초신경병증 양상·신경생리검사 결과 (유홍근)
-· 7/29 병동 환자 교육: 신경근육질환 입원환자 진찰·진단 과정 (박예지, 박은지)
-· 7/30 전공의 교육: 뇌수막 이상 관련 질환 (송준규, 박예지, 박은지, 유홍근)
-[김용성 6건]
-· 7/6 신경생리검사 판독 및 교육(평가 3점) (송준규)
-· 7/13 Peroneal neuropathy 북리딩(Preston 25), 발표·토론(평가 1점) (송준규, 박예지, 박은지, 유홍근)
-· 7/13 신경생리검사 판독 및 교육(평가 3점) (송준규)
-· 7/20 신경생리검사 판독 및 교육(평가 3점) (송준규)
-· 7/27 Femoral neuropathy 북리딩(Preston 26), 발표·토론(평가 1점) (송준규, 박예지, 박은지, 유홍근)
-· 7/27 신경생리검사 판독 및 교육(평가 3점) (송준규)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="17.25" customHeight="1" s="21">
+          <t>총 21건
+· 현장 교육 7건: 외래(운동신경세포병·상완신경총병증·말초신경병증 등), 응급실(두통·어지럼)
+· 임상 교육 6건: 신경생리검사 판독, 치매 인지기능검사 해석, 급성뇌경색 평가
+· 환자 교육 1건: 병동 신경근육질환 환자 진찰·진단
+· 이론 교육 7건: 신경해부(뇌실·뇌척수액·뇌막), 신경전달물질, 말초신경병증 북리딩</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1" s="21">
       <c r="A3" s="23" t="n"/>
       <c r="B3" s="7" t="n">
         <v>2</v>
@@ -729,7 +711,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="49.5" customHeight="1" s="21">
+    <row r="4" ht="24" customHeight="1" s="21">
       <c r="A4" s="23" t="n"/>
       <c r="B4" s="7" t="n">
         <v>3</v>
@@ -741,12 +723,11 @@
       </c>
       <c r="D4" s="22" t="inlineStr">
         <is>
-          <t>[성원재 1건]
-· 7/14 지도전문의-전공의 간담회: 연차별 2학기 전공의 스케줄·휴가 일정 조정 완료 (송준규, 박예지, 유홍근)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="132" customHeight="1" s="21">
+          <t>총 1건: 지도전문의-전공의 간담회: 2학기 스케줄·휴가 조정</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1" s="21">
       <c r="A5" s="23" t="n"/>
       <c r="B5" s="7" t="n">
         <v>4</v>
@@ -758,15 +739,11 @@
       </c>
       <c r="D5" s="22" t="inlineStr">
         <is>
-          <t>[성원재 4건]
-· 7/3 수련·근무/학습·역량: 9월 전공의 교대·업무 변경, 연차별 주 1회 당직 변경 안내 (박예지, 박은지, 유홍근)
-· 7/10 수련·근무/학습·역량: 수련 상황, 하계 휴가 일정, 휴가 중 업무 전가 방지 약속 (송준규, 박예지, 박은지, 유홍근)
-· 7/24 학습·역량: 본원 입원환자 접근 방법, 수석 전공의 중심 입원환자 리뷰·발표 (송준규, 박예지, 박은지, 유홍근)
-· 7/31 진로·진학: 의국 출신 전문의 진로 안내 (송준규, 박예지, 박은지, 유홍근)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="17.25" customHeight="1" s="21">
+          <t>총 4건 (분야: 수련·근무 2, 학습·역량 3, 진로·진학 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1" s="21">
       <c r="A6" s="24" t="n"/>
       <c r="B6" s="1" t="n">
         <v>5</v>
@@ -782,7 +759,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="231" customHeight="1" s="21">
+    <row r="7" ht="74" customHeight="1" s="21">
       <c r="A7" s="1" t="inlineStr">
         <is>
           <t>’26.8월</t>
@@ -798,22 +775,14 @@
       </c>
       <c r="D7" s="22" t="inlineStr">
         <is>
-          <t>[성원재 6건]
-· 8/3 외래 진료 교육: 경추·요추 근뿌리병증 병력 청취·진찰·검사 해석(평가 4점) (송준규)
-· 8/6 전공의 교육: 뇌혈관 해부학 강의(Chap 8) (송준규, 박예지, 박은지, 유홍근)
-· 8/10 외래 진료 교육: 루게릭병 환자 외래 진료 및 보호자 교육 (송준규)
-· 8/12 응급실 진료 지도: 두통환자 문진·진찰·영상 해석, 외래 추적 시 주의점 (박예지, 박은지)
-· 8/13 전공의 교육: 본원 내원 뇌졸중 환자 증례 보고 및 시사점 논의 (송준규, 박예지, 박은지)
-· 8/31 외래 진료 교육: 중증근무력증 환자 평가(MG-ADL 등), Level 2 (유홍근)
-[김용성 4건]
-· 8/10 Tarsal tunnel syndrome 북리딩(Preston 27), 발표·토론(평가 1점) (송준규, 박예지, 박은지, 유홍근)
-· 8/10 신경생리검사 판독 및 교육(평가 3점) (송준규)
-· 8/28 Facial and Trigeminal neuropathy 북리딩(Preston 28), 발표·토론(평가 1점) (송준규, 박예지, 박은지, 유홍근)
-· 8/28 신경생리검사 판독 및 교육(평가 3점) (송준규)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="17.25" customHeight="1" s="21">
+          <t>총 10건
+· 현장 교육 4건: 외래(근뿌리병증·루게릭병·중증근무력증), 응급실(두통)
+· 임상 교육 2건: 신경생리검사 판독
+· 이론 교육 4건: 뇌혈관 해부, 뇌졸중 증례 논의, 말초신경병증 북리딩</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1" s="21">
       <c r="A8" s="23" t="n"/>
       <c r="B8" s="7" t="n">
         <v>2</v>
@@ -829,7 +798,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="17.25" customHeight="1" s="21">
+    <row r="9" ht="24" customHeight="1" s="21">
       <c r="A9" s="23" t="n"/>
       <c r="B9" s="7" t="n">
         <v>3</v>
@@ -845,7 +814,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="66" customHeight="1" s="21">
+    <row r="10" ht="24" customHeight="1" s="21">
       <c r="A10" s="23" t="n"/>
       <c r="B10" s="7" t="n">
         <v>4</v>
@@ -857,13 +826,11 @@
       </c>
       <c r="D10" s="22" t="inlineStr">
         <is>
-          <t>[성원재 2건]
-· 8/5 수련·근무/생활·심리: 개별 면담으로 고충·학습 현황 청취, 적극적 학습 권유 (송준규, 박예지, 박은지, 유홍근)
-· 8/14 기타: 의정사태 이후 변화된 환경에 대한 사직 전공의 고충 청취 (송준규, 박예지, 박은지)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="17.25" customHeight="1" s="21">
+          <t>총 2건 (분야: 수련·근무 1, 생활·심리 1, 기타 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1" s="21">
       <c r="A11" s="24" t="n"/>
       <c r="B11" s="1" t="n">
         <v>5</v>
@@ -879,7 +846,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="346.5" customHeight="1" s="21">
+    <row r="12" ht="91" customHeight="1" s="21">
       <c r="A12" s="1" t="inlineStr">
         <is>
           <t>’26.9월</t>
@@ -895,29 +862,14 @@
       </c>
       <c r="D12" s="22" t="inlineStr">
         <is>
-          <t>[성원재 13건]
-· 9/1 전공의 교육: 척수 해부학(Chap 9) (박은지, 신정욱)
-· 9/2 치매안심센터 진료 교육: CIST, CERAD 평가 방법·결과 의의, Level 1 (박은지)
-· 9/7 외래 진료 교육: ALS 병기 평가(ALSFRS-R, King's stage), Level 4 (박은지)
-· 9/8 전공의 교육: 척수 부위 질환 해부학 지식 및 강의 (신정욱, 박은지)
-· 9/9 응급실 진료 지도: 급성뇌경색 처치·치료 알고리즘, Level 4 이상 (박은지)
-· 9/14 외래 진료 교육: NMOSD 환자 병력 청취·신경계 진찰, Level 4 (박은지)
-· 9/15 전공의 교육: NMOSD 증례 및 진단 기준 강의 (신정욱, 박은지)
-· 9/16 치매안심센터 진료 교육: 치매/경도인지장애 병력 청취·CDR 평가, Level 3 (박은지)
-· 9/17 전공의 교육: 레비소체치매 증례 소개 및 주요 증상(참석 강성우 포함) (박은지, 신정욱)
-· 9/21 외래 진료 교육: 외래 진료 참관 (유홍근)
-· 9/23 치매안심센터 진료 교육: 지역사회 경도인지장애·치매 환자 관리, 진료 참관 (신정욱)
-· 9/28 외래 진료 교육: 영양결핍 신경계 질환 진찰·병력 청취·검사 (박은지)
-· 9/29 전공의 교육: Lateral medullary syndrome 증례(참석 정수 포함) (박은지, 신정욱)
-[김용성 4건]
-· 9/7 신경생리검사 판독 및 교육, 2시간(평가 3점) (신정욱)
-· 9/14 신경생리검사 판독 및 교육, 2시간(평가 3점) (신정욱)
-· 9/21 Polyneuropathy 북리딩(Preston), 발표·토론(평가 1점) (신정욱, 박은지)
-· 9/21 신경생리검사 판독 및 교육, 2시간(평가 3점) (신정욱)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="33" customHeight="1" s="21">
+          <t>총 17건
+· 현장 교육 5건: 외래(ALS·NMOSD·영양결핍 신경질환), 응급실(급성뇌경색)
+· 임상 교육 6건: 치매안심센터 진료, 신경생리검사 판독
+· 이론 교육 6건: 척수 해부, NMOSD·레비소체치매·Lateral medullary syndrome 증례, 북리딩</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1" s="21">
       <c r="A13" s="23" t="n"/>
       <c r="B13" s="7" t="n">
         <v>2</v>
@@ -929,12 +881,11 @@
       </c>
       <c r="D13" s="22" t="inlineStr">
         <is>
-          <t>[성원재 1건]
-· 9/22 원내 컨퍼런스 - 증례 발표: 박은지 NMOSD 증례 및 치료 가이드라인 (신정욱, 박은지)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="82.5" customHeight="1" s="21">
+          <t>총 1건: 원내 컨퍼런스 증례 발표(NMOSD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1" s="21">
       <c r="A14" s="23" t="n"/>
       <c r="B14" s="7" t="n">
         <v>3</v>
@@ -946,13 +897,11 @@
       </c>
       <c r="D14" s="22" t="inlineStr">
         <is>
-          <t>[성원재 2건]
-· 9/3 2학기 학회(심포지움) 참석 스케줄 논의: WSC, MDS, IC-KNA 가급적 참석 결정(참석 김영서) (신정욱, 박은지)
-· 9/10 2학기 원내 학술활동 일정 논의: 토픽·저널 컨퍼런스, 지도전문의 강의 스케줄 가안 확정(참석 김영서) ((대상 전공의 미기재))</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="99" customHeight="1" s="21">
+          <t>총 2건: 2학기 학회 참석 일정, 원내 학술활동 일정 논의</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" s="21">
       <c r="A15" s="23" t="n"/>
       <c r="B15" s="7" t="n">
         <v>4</v>
@@ -964,15 +913,11 @@
       </c>
       <c r="D15" s="22" t="inlineStr">
         <is>
-          <t>[성원재 4건]
-· 9/4 수련·근무/학습·역량: 2학기 수련·업무 방향, 교육활동·임상신경생리검사 학습 주안점 (신정욱, 박은지)
-· 9/11 진로·진학: 전문의 시험 이후 일정, 전문적 업무분장 (신정욱, 박은지)
-· 9/18 수련·근무: 당직 애로사항 청취, 지도전문의에게 도움 요청 지도 (신정욱, 박은지)
-· 9/21 수련·근무: 수련 현황, 업무 분장, 당직 체계 논의 (박은지)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="17.25" customHeight="1" s="21">
+          <t>총 4건 (분야: 수련·근무 3, 학습·역량 1, 진로·진학 1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1" s="21">
       <c r="A16" s="24" t="n"/>
       <c r="B16" s="1" t="n">
         <v>5</v>
